--- a/docs/mode_4_algorithm.xlsx
+++ b/docs/mode_4_algorithm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mauritshartman/RUDE_energy/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9BA812-AF15-674C-8D93-3CB83510FFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00B9706-4DAE-FF49-A7B0-C914A1FA5B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1640" windowWidth="37880" windowHeight="25500" xr2:uid="{E6BD9C62-C3AC-2548-A5EF-370011D8CB78}"/>
+    <workbookView xWindow="-38620" yWindow="700" windowWidth="37900" windowHeight="26820" xr2:uid="{E6BD9C62-C3AC-2548-A5EF-370011D8CB78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -110,15 +110,9 @@
     <t>Close to PGmax</t>
   </si>
   <si>
-    <t>Notclose to PGmax</t>
-  </si>
-  <si>
     <t>Some solar power, but not enough to fully cover demand (battery charging and/or Pother), so additional charging from grid necessary. NO ACTION</t>
   </si>
   <si>
-    <t>Max battery discharging and/or high solar power generation. Supplying to the grid at PGmax limit could be desirable to maximize profit. ACTION: limit solar power first, then limit battery discharge</t>
-  </si>
-  <si>
     <t>During each control loop cycle, the desired power levels from the schedule are applied for each controlled device, followed by a:</t>
   </si>
   <si>
@@ -179,10 +173,16 @@
     <t>Must be battery discharging. Supplying to the grid is undesirable, but could be possible to create battery capacity to profit from even lower prices later.  NO ACTION</t>
   </si>
   <si>
-    <t>Most likely high solar power generation or some battery discharging. Supplying to the grid with negative prices is highly undesirable. Unlikely that the schedule warrants battery charging ACTION: limit solar power to net zero at grid</t>
-  </si>
-  <si>
-    <t>Most likely high solar power generation or some battery discharging. Supplying to the grid at PGmax limit is highly undesirable. Unlikely that the schedule warrants battery charging ACTION: limit solar power to net zero at grid</t>
+    <t>Most likely high solar power generation or some battery discharging. Supplying to the grid at PGmax limit is highly undesirable. Unlikely that the schedule warrants battery discharging ACTION: limit solar power to net PGmin</t>
+  </si>
+  <si>
+    <t>Most likely high solar power generation or some battery discharging. Supplying to the grid with negative prices is highly undesirable. Unlikely that the schedule warrants battery discharging ACTION: limit solar power to net PGmin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max battery discharging and/or high solar power generation. Supplying to the grid at PGmax limit could be desirable to maximize profit. ACTION: limit battery discharge first (iff discharging), then solar power to stay close to PGmax </t>
+  </si>
+  <si>
+    <t>Not close to PGmax</t>
   </si>
 </sst>
 </file>
@@ -318,28 +318,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -357,6 +339,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,20 +713,20 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -734,7 +734,7 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -744,23 +744,23 @@
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12" t="s">
+      <c r="E9" s="17"/>
+      <c r="F9" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="12"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -773,171 +773,171 @@
         <v>22</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="9" t="s">
+      <c r="F11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="19"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19"/>
+      <c r="B13" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="20"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="18" t="s">
+      <c r="D15" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11" t="s">
+      <c r="G16" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19"/>
+      <c r="B17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="20"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="17" t="s">
+      <c r="D18" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="18" t="s">
+      <c r="F18" s="13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="G18" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
